--- a/TECH.xlsx
+++ b/TECH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\EFS\EW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\Emperor Wars Mod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F82C714-11F3-4796-9E5B-4FD07B20148F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6D0123-F3EA-48D1-BD17-7C0EC770FC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18954,7 +18954,7 @@
         <v>22</v>
       </c>
       <c r="S272">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T272" t="s">
         <v>503</v>
@@ -19757,7 +19757,7 @@
         <v>5</v>
       </c>
       <c r="R285">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S285">
         <v>-1</v>
@@ -19819,7 +19819,7 @@
         <v>5</v>
       </c>
       <c r="R286">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S286">
         <v>-1</v>
@@ -19881,7 +19881,7 @@
         <v>5</v>
       </c>
       <c r="R287">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="S287">
         <v>-1</v>
@@ -20501,7 +20501,7 @@
         <v>5</v>
       </c>
       <c r="R297">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S297">
         <v>1</v>
@@ -20563,7 +20563,7 @@
         <v>5</v>
       </c>
       <c r="R298">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S298">
         <v>2</v>
@@ -20625,7 +20625,7 @@
         <v>5</v>
       </c>
       <c r="R299">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S299">
         <v>3</v>
@@ -21186,7 +21186,7 @@
         <v>59</v>
       </c>
       <c r="S308">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T308" t="s">
         <v>503</v>
@@ -24968,7 +24968,7 @@
         <v>118</v>
       </c>
       <c r="S369">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="T369" t="s">
         <v>503</v>
@@ -25399,7 +25399,7 @@
         <v>5</v>
       </c>
       <c r="R376">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="S376">
         <v>-1</v>
